--- a/ЛР2-3_Объем_рынка/Excel/ЛР2-3_7_поисковый_спрос_TableMind.xlsx
+++ b/ЛР2-3_Объем_рынка/Excel/ЛР2-3_7_поисковый_спрос_TableMind.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-3ab569\ЛР2-3_Объем_рынка\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-57ce20\ЛР2-3_Объем_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDDD1B7C-FCBC-42D4-85D0-F9EF43988BA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01CD81C3-80A0-4AAA-912D-BD7F386BD4AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="368" yWindow="368" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Методика" sheetId="1" r:id="rId1"/>
@@ -591,10 +591,10 @@
     <t>Россия 225, Беларусь 149, 2018-2026 (данные ЛР1)</t>
   </si>
   <si>
-    <t>Рекламных кабинетов нет: ДОСНЯТЬ</t>
-  </si>
-  <si>
-    <t>Сайта и CRM пока нет: ДОСНЯТЬ после MVP</t>
+    <t>Рекламных кабинетов нет: использованы модельные показатели (допущение Д-33)</t>
+  </si>
+  <si>
+    <t>Сайта и CRM пока нет: использованы модельные замеры (допущение Д-32)</t>
   </si>
 </sst>
 </file>
@@ -1539,7 +1539,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" ht="27">
       <c r="A8" s="2" t="s">
         <v>144</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" ht="27">
       <c r="A9" s="2" t="s">
         <v>146</v>
       </c>
@@ -3874,7 +3874,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="27">
+    <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
         <v>120</v>
       </c>

--- a/ЛР2-3_Объем_рынка/Excel/ЛР2-3_7_поисковый_спрос_TableMind.xlsx
+++ b/ЛР2-3_Объем_рынка/Excel/ЛР2-3_7_поисковый_спрос_TableMind.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-57ce20\ЛР2-3_Объем_рынка\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-89518d\ЛР2-3_Объем_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01CD81C3-80A0-4AAA-912D-BD7F386BD4AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BBEA137-2BE7-4C0D-8236-ABD6A8991C42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -591,10 +591,10 @@
     <t>Россия 225, Беларусь 149, 2018-2026 (данные ЛР1)</t>
   </si>
   <si>
-    <t>Рекламных кабинетов нет: использованы модельные показатели (допущение Д-33)</t>
-  </si>
-  <si>
-    <t>Сайта и CRM пока нет: использованы модельные замеры (допущение Д-32)</t>
+    <t>Рекламных кабинетов нет: использованы расчетные показатели (допущение Д-33)</t>
+  </si>
+  <si>
+    <t>Сайта и CRM пока нет: использованы расчетные замеры (допущение Д-32)</t>
   </si>
 </sst>
 </file>

--- a/ЛР2-3_Объем_рынка/Excel/ЛР2-3_7_поисковый_спрос_TableMind.xlsx
+++ b/ЛР2-3_Объем_рынка/Excel/ЛР2-3_7_поисковый_спрос_TableMind.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-continuation-57ce20\ЛР2-3_Объем_рынка\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-project-continuation-447426\ЛР2-3_Объем_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01CD81C3-80A0-4AAA-912D-BD7F386BD4AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435BFD43-0878-49A6-A7B8-0771A0AA71D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
     <sheet name="08_Дашборд" sheetId="9" r:id="rId9"/>
     <sheet name="09_Источники" sheetId="10" r:id="rId10"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -504,7 +504,7 @@
     <t>1: годовой чек уже учитывает платежи в течение года</t>
   </si>
   <si>
-    <t>Веса источников 0,5/0,5 (допущение Д-07 ЛР1)</t>
+    <t>Веса источников 0,5/0,5 (допущение Д-06 ЛР1)</t>
   </si>
   <si>
     <t>excel audit</t>
@@ -591,10 +591,10 @@
     <t>Россия 225, Беларусь 149, 2018-2026 (данные ЛР1)</t>
   </si>
   <si>
-    <t>Рекламных кабинетов нет: использованы модельные показатели (допущение Д-33)</t>
-  </si>
-  <si>
-    <t>Сайта и CRM пока нет: использованы модельные замеры (допущение Д-32)</t>
+    <t>Рекламных кабинетов нет: ДОСНЯТЬ</t>
+  </si>
+  <si>
+    <t>Сайта и CRM пока нет: ДОСНЯТЬ после MVP</t>
   </si>
 </sst>
 </file>
@@ -862,7 +862,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-E45F-45D5-BD42-9E5D4A13022D}"/>
+              <c16:uniqueId val="{00000000-0B2D-438A-BB92-97D675C2CA45}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1539,7 +1539,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="27">
+    <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
         <v>144</v>
       </c>
@@ -1556,7 +1556,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="27">
+    <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
         <v>146</v>
       </c>
@@ -3874,7 +3874,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" ht="27">
       <c r="A9" s="2" t="s">
         <v>120</v>
       </c>

--- a/ЛР2-3_Объем_рынка/Excel/ЛР2-3_7_поисковый_спрос_TableMind.xlsx
+++ b/ЛР2-3_Объем_рынка/Excel/ЛР2-3_7_поисковый_спрос_TableMind.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-project-continuation-447426\ЛР2-3_Объем_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435BFD43-0878-49A6-A7B8-0771A0AA71D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E91D17C2-7E8B-46C4-A91D-9BF856A51948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -862,7 +862,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-0B2D-438A-BB92-97D675C2CA45}"/>
+              <c16:uniqueId val="{00000000-B757-4A19-A572-B44E3C584850}"/>
             </c:ext>
           </c:extLst>
         </c:ser>

--- a/ЛР2-3_Объем_рынка/Excel/ЛР2-3_7_поисковый_спрос_TableMind.xlsx
+++ b/ЛР2-3_Объем_рынка/Excel/ЛР2-3_7_поисковый_спрос_TableMind.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TableMind_EB\.claude\worktrees\handoff-project-continuation-447426\ЛР2-3_Объем_рынка\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28F06425-5C6C-4459-A10F-2BF1C3EF81AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5AD6B78-6B5D-43D7-89C9-E58A9B387B4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2205" yWindow="458" windowWidth="12022" windowHeight="10972" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="11625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Методика" sheetId="1" r:id="rId1"/>
@@ -43,17 +43,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="184">
-  <si>
-    <t>Excel-шаблон: оценка объема рынка через поисковый спрос</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="185">
   <si>
     <t>Назначение</t>
   </si>
   <si>
-    <t>Шаблон переводит поисковый спрос в оценку потенциальных переходов, заявок, продаж и денежного объема рынка.</t>
-  </si>
-  <si>
     <t>Логика</t>
   </si>
   <si>
@@ -75,9 +69,6 @@
     <t>Как работать</t>
   </si>
   <si>
-    <t>Заполните листы 01–04, проверьте расчет на листах 05–07 и используйте лист 08 для итогового вывода.</t>
-  </si>
-  <si>
     <t>Порядок заполнения</t>
   </si>
   <si>
@@ -90,9 +81,6 @@
     <t>Лист</t>
   </si>
   <si>
-    <t>Заполнить параметры рынка и конверсий</t>
-  </si>
-  <si>
     <t>01_Параметры</t>
   </si>
   <si>
@@ -159,9 +147,6 @@
     <t>текст</t>
   </si>
   <si>
-    <t>Можно заменить на страну, область или город.</t>
-  </si>
-  <si>
     <t>Период анализа</t>
   </si>
   <si>
@@ -249,18 +234,12 @@
     <t>Инструментальный спрос</t>
   </si>
   <si>
-    <t>Данные Google Trends: месячный индекс интереса</t>
-  </si>
-  <si>
     <t>Месяц</t>
   </si>
   <si>
     <t>Средний индекс GT</t>
   </si>
   <si>
-    <t>Данные Яндекс Вордстат: частотность запросов</t>
-  </si>
-  <si>
     <t>Суммарная частотность</t>
   </si>
   <si>
@@ -285,9 +264,6 @@
     <t>Оценка уровня</t>
   </si>
   <si>
-    <t>Цифровая воронка: перевод поискового спроса в продажи и выручку</t>
-  </si>
-  <si>
     <t>Показатель</t>
   </si>
   <si>
@@ -408,9 +384,6 @@
     <t>Диапазон годовой выручки</t>
   </si>
   <si>
-    <t>Осторожный — оптимистичный сценарий.</t>
-  </si>
-  <si>
     <t>Уровень интереса</t>
   </si>
   <si>
@@ -489,9 +462,6 @@
     <t>Фактические конверсии, заявки, средний чек</t>
   </si>
   <si>
-    <t>EUR</t>
-  </si>
-  <si>
     <t>Россия и Беларусь (Вордстат; контрольный русскоязычный сегмент), Google Trends - весь мир</t>
   </si>
   <si>
@@ -501,9 +471,6 @@
     <t>Выручка первого года на платящего (Д-09)</t>
   </si>
   <si>
-    <t>1: годовой чек уже учитывает платежи в течение года</t>
-  </si>
-  <si>
     <t>Веса источников 0,5/0,5 (допущение Д-06 ЛР1)</t>
   </si>
   <si>
@@ -591,10 +558,46 @@
     <t>Россия 225, Беларусь 149, 2018-2026 (данные ЛР1)</t>
   </si>
   <si>
-    <t>Рекламных кабинетов нет: ДОСНЯТЬ</t>
-  </si>
-  <si>
-    <t>Сайта и CRM пока нет: ДОСНЯТЬ после MVP</t>
+    <t>Оценка объема рынка через поисковый спрос</t>
+  </si>
+  <si>
+    <t>Расчет переводит поисковый спрос в оценку потенциальных переходов, заявок, продаж и денежного объема рынка.</t>
+  </si>
+  <si>
+    <t>Территория расчета</t>
+  </si>
+  <si>
+    <t>у.е.</t>
+  </si>
+  <si>
+    <t>1 - годовой чек уже учитывает платежи в течение года</t>
+  </si>
+  <si>
+    <t>Данные Google Trends - месячный индекс интереса</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Данные Яндекс Вордстат - частотность запросов</t>
+  </si>
+  <si>
+    <t>Цифровая воронка - перевод поискового спроса в продажи и выручку</t>
+  </si>
+  <si>
+    <t>Осторожный - оптимистичный сценарий.</t>
+  </si>
+  <si>
+    <t>Рекламные кабинеты не подключены, тестовые кампании запланированы после запуска MVP</t>
+  </si>
+  <si>
+    <t>Сайт и CRM запускаются вместе с MVP, данные появятся после запуска</t>
+  </si>
+  <si>
+    <t>Листы 01–04, проверьте расчет на листах 05–07 и используйте лист 08 для итогового вывода.</t>
+  </si>
+  <si>
+    <t>Параметры рынка и конверсий</t>
   </si>
 </sst>
 </file>
@@ -607,7 +610,11 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -616,23 +623,32 @@
       <b/>
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Carlito"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Carlito"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Carlito"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF1F3864"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
   <fills count="7">
@@ -644,31 +660,36 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0B1F33"/>
+        <fgColor rgb="FF1F4E79"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9EAF7"/>
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E79"/>
+        <fgColor rgb="FF2E75B6"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2F0D9"/>
+        <fgColor rgb="FFEAF1FB"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -676,68 +697,1380 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9DC3E6"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9DC3E6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9DC3E6"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9DC3E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9DC3E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9DC3E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9DC3E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9DC3E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF9DC3E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9DC3E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9DC3E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9DC3E6"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="6" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="72">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="none"/>
+      </font>
+      <alignment vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -769,9 +2102,16 @@
           <c:tx>
             <c:v>Сводный индекс спроса</c:v>
           </c:tx>
+          <c:marker>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="1F4E79"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>'05_Нормализация'!$A$4:$A$15</c:f>
+              <c:f>'05_Нормализация'!$A$3:$A$14</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm</c:formatCode>
                 <c:ptCount val="12"/>
@@ -816,7 +2156,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'05_Нормализация'!$F$4:$F$15</c:f>
+              <c:f>'05_Нормализация'!$F$3:$F$14</c:f>
               <c:numCache>
                 <c:formatCode>0.0</c:formatCode>
                 <c:ptCount val="12"/>
@@ -941,12 +2281,26 @@
     <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
+    <a:solidFill>
+      <a:sysClr val="window" lastClr="FFFFFF"/>
+    </a:solidFill>
     <a:ln w="9525">
-      <a:solidFill>
-        <a:srgbClr val="D9D9D9"/>
-      </a:solidFill>
+      <a:noFill/>
       <a:prstDash val="solid"/>
+      <a:round/>
     </a:ln>
+    <a:effectLst/>
+    <a:extLst>
+      <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+        <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+          <a:solidFill>
+            <a:srgbClr val="D9D9D9"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+        </a14:hiddenLine>
+      </a:ext>
+    </a:extLst>
   </c:spPr>
   <c:printSettings>
     <c:headerFooter/>
@@ -960,16 +2314,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
+      <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1779587</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>44450</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -998,107 +2352,107 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SemanticCore" displayName="SemanticCore" ref="A3:J13">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="SemanticCore" displayName="SemanticCore" ref="A2:J12" headerRowDxfId="71" dataDxfId="70" totalsRowDxfId="69">
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Запрос"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Группа"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Намерение"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Регион"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Частотность Wordstat / мес."/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Индекс Google Trends (ближайший англоязычный аналог, среднее 12 мес.)"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Вес релевантности"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Коммерческая близость"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Взвешенный спрос"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="68"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Запрос" dataDxfId="67"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Группа" dataDxfId="66"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Намерение" dataDxfId="65"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Регион" dataDxfId="64"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Частотность Wordstat / мес." dataDxfId="63"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Индекс Google Trends (ближайший англоязычный аналог, среднее 12 мес.)" dataDxfId="62"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Вес релевантности" dataDxfId="61"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Коммерческая близость" dataDxfId="60"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Взвешенный спрос" dataDxfId="59"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="GoogleTrends" displayName="GoogleTrends" ref="A3:G15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="GoogleTrends" displayName="GoogleTrends" ref="A2:G14" headerRowDxfId="58" dataDxfId="57" totalsRowDxfId="56">
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Месяц"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="excel audit"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="spreadsheet audit"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="excel formula checker"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="financial model audit"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Средний индекс GT"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Комментарий"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Месяц" dataDxfId="55"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="excel audit" dataDxfId="54"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="spreadsheet audit" dataDxfId="53"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="excel formula checker" dataDxfId="52"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0100-000005000000}" name="financial model audit" dataDxfId="51"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0100-000006000000}" name="Средний индекс GT" dataDxfId="50"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0100-000007000000}" name="Комментарий" dataDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Wordstat" displayName="Wordstat" ref="A3:H15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="Wordstat" displayName="Wordstat" ref="A2:H14" headerRowDxfId="48" dataDxfId="47" totalsRowDxfId="46">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Месяц"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Услуговые и аудиторские запросы"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Проблемные запросы (ошибки)"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="AI-инструменты"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Проверка формул"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Суммарная частотность"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Коммерческий коэффициент (инструментальные и услуговые запросы, ЛР1)"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Взвешенная частотность"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Месяц" dataDxfId="45"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Услуговые и аудиторские запросы" dataDxfId="44"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Проблемные запросы (ошибки)" dataDxfId="43"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="AI-инструменты" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="Проверка формул" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0200-000006000000}" name="Суммарная частотность" dataDxfId="40"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0200-000007000000}" name="Коммерческий коэффициент (инструментальные и услуговые запросы, ЛР1)" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0200-000008000000}" name="Взвешенная частотность" dataDxfId="38"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="NormalizedDemand" displayName="NormalizedDemand" ref="A3:H15">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="NormalizedDemand" displayName="NormalizedDemand" ref="A2:H14" headerRowDxfId="37" dataDxfId="36" totalsRowDxfId="35">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Месяц"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Средний индекс GT"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Нормированный GT"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Взвешенная частотность WS"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Нормированный WS"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Сводный индекс спроса"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Оценка уровня"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Комментарий"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="Месяц" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="Средний индекс GT" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Нормированный GT" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0300-000004000000}" name="Взвешенная частотность WS" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0300-000005000000}" name="Нормированный WS" dataDxfId="30"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Сводный индекс спроса" dataDxfId="29"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Оценка уровня" dataDxfId="28"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Комментарий" dataDxfId="27"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Funnel" displayName="Funnel" ref="A3:E14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{00000000-000C-0000-FFFF-FFFF04000000}" name="Funnel" displayName="Funnel" ref="A2:E13" headerRowDxfId="26" dataDxfId="25" totalsRowDxfId="24">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Показатель"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Осторожный"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Базовый"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Оптимистичный"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Комментарий"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0400-000001000000}" name="Показатель" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0400-000002000000}" name="Осторожный" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0400-000003000000}" name="Базовый" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0400-000004000000}" name="Оптимистичный" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0400-000005000000}" name="Комментарий" dataDxfId="19"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Scenarios" displayName="Scenarios" ref="A3:H6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{00000000-000C-0000-FFFF-FFFF05000000}" name="Scenarios" displayName="Scenarios" ref="A2:H5" headerRowDxfId="18" dataDxfId="17" totalsRowDxfId="16">
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Сценарий"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Переходы / мес."/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Заявки / мес."/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Продажи / мес."/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Средний чек"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Выручка / мес."/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Выручка / год"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="Интерпретация"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0500-000001000000}" name="Сценарий" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0500-000002000000}" name="Переходы / мес." dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0500-000003000000}" name="Заявки / мес." dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0500-000004000000}" name="Продажи / мес." dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0500-000005000000}" name="Средний чек" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0500-000006000000}" name="Выручка / мес." dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0500-000007000000}" name="Выручка / год" dataDxfId="9"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0500-000008000000}" name="Интерпретация" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Sources" displayName="Sources" ref="A3:E9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{00000000-000C-0000-FFFF-FFFF06000000}" name="Sources" displayName="Sources" ref="A2:E8" headerRowDxfId="7" dataDxfId="6" totalsRowDxfId="5">
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Источник"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Что брать"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Период / регион"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Дата фиксации"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="Ссылка / примечание"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0600-000001000000}" name="Источник" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0600-000002000000}" name="Что брать" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0600-000003000000}" name="Период / регион" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0600-000004000000}" name="Дата фиксации" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0600-000005000000}" name="Ссылка / примечание" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1253,324 +2607,400 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="66.0625" customWidth="1"/>
-    <col min="2" max="2" width="45" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="1" max="1" width="24.5625" customWidth="1"/>
+    <col min="2" max="2" width="52.5625" customWidth="1"/>
+    <col min="3" max="3" width="20.375" customWidth="1"/>
+    <col min="4" max="8" width="10.5625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.649999999999999">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:8" ht="20" customHeight="1">
+      <c r="A1" s="49" t="s">
+        <v>171</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+    </row>
+    <row r="2" spans="1:8" ht="28.5">
+      <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-    </row>
-    <row r="3" spans="1:8" ht="40.5">
-      <c r="A3" s="1" t="s">
+      <c r="B2" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" ht="42.75">
+      <c r="A3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="7" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="40.5">
-      <c r="A4" s="1" t="s">
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:8" ht="42.75">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="7" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="54">
-      <c r="A5" s="1" t="s">
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" ht="28.5">
+      <c r="A5" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="7" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="40.5">
-      <c r="A6" s="1" t="s">
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" ht="28.5">
+      <c r="A6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:8" ht="20" customHeight="1">
+      <c r="A7" s="51" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="40.5">
-      <c r="A7" s="1" t="s">
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="50"/>
+    </row>
+    <row r="8" spans="1:8" ht="14.25">
+      <c r="A8" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B8" s="8" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="22" t="s">
+      <c r="C8" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-    </row>
-    <row r="10" spans="1:8" ht="13.9">
-      <c r="A10" s="3" t="s">
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" ht="14.25">
+      <c r="A9" s="9">
+        <v>1</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="C9" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" ht="14.25">
+      <c r="A10" s="9">
+        <v>2</v>
+      </c>
+      <c r="B10" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="16" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11">
-        <v>1</v>
-      </c>
-      <c r="B11" t="s">
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" ht="14.25">
+      <c r="A11" s="9">
+        <v>3</v>
+      </c>
+      <c r="B11" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="16" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12">
-        <v>2</v>
-      </c>
-      <c r="B12" t="s">
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" ht="14.25">
+      <c r="A12" s="9">
+        <v>4</v>
+      </c>
+      <c r="B12" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="16" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13">
-        <v>3</v>
-      </c>
-      <c r="B13" t="s">
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:8" ht="14.25">
+      <c r="A13" s="9">
+        <v>5</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="16" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14">
-        <v>4</v>
-      </c>
-      <c r="B14" t="s">
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="1:8" ht="14.25">
+      <c r="A14" s="9">
+        <v>6</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="16" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15">
-        <v>5</v>
-      </c>
-      <c r="B15" t="s">
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+    </row>
+    <row r="15" spans="1:8" ht="14.25">
+      <c r="A15" s="9">
+        <v>7</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="16" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16">
-        <v>6</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+    </row>
+    <row r="16" spans="1:8" ht="14.25">
+      <c r="A16" s="10">
+        <v>8</v>
+      </c>
+      <c r="B16" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="11" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17">
-        <v>7</v>
-      </c>
-      <c r="B17" t="s">
-        <v>27</v>
-      </c>
-      <c r="C17" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18">
-        <v>8</v>
-      </c>
-      <c r="B18" t="s">
-        <v>29</v>
-      </c>
-      <c r="C18" t="s">
-        <v>30</v>
-      </c>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A7:H7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="42.6875" customWidth="1"/>
-    <col min="2" max="2" width="48" customWidth="1"/>
-    <col min="3" max="3" width="14.25" customWidth="1"/>
-    <col min="4" max="4" width="12.9375" customWidth="1"/>
-    <col min="5" max="5" width="58" customWidth="1"/>
+    <col min="1" max="1" width="27.6875" customWidth="1"/>
+    <col min="2" max="3" width="52.5625" customWidth="1"/>
+    <col min="4" max="4" width="17.1875" customWidth="1"/>
+    <col min="5" max="5" width="52.5625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="17.649999999999999">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:5" ht="20" customHeight="1">
+      <c r="A1" s="49" t="s">
+        <v>115</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+    </row>
+    <row r="2" spans="1:5" ht="14.25">
+      <c r="A2" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="14.25">
+      <c r="A3" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>169</v>
+      </c>
+      <c r="D3" s="47">
+        <v>46298</v>
+      </c>
+      <c r="E3" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-    </row>
-    <row r="3" spans="1:5" ht="27.75">
-      <c r="A3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:5" ht="14.25">
+      <c r="A4" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B4" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C4" s="22" t="s">
         <v>127</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D4" s="47">
+        <v>46298</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="3" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="14.25">
+      <c r="A5" s="3" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="27">
-      <c r="A4" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="C5" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D5" s="47">
+        <v>46298</v>
+      </c>
+      <c r="E5" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="D4" s="19">
+    </row>
+    <row r="6" spans="1:5" ht="14.25">
+      <c r="A6" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="D6" s="47">
         <v>46298</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="27">
-      <c r="A5" s="2" t="s">
+      <c r="E6" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="B5" s="2" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="28.5">
+      <c r="A7" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D5" s="19">
+      <c r="C7" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="47">
         <v>46298</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E7" s="7" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="28.5">
+      <c r="A8" s="4" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="54">
-      <c r="A6" s="2" t="s">
+      <c r="B8" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="D6" s="19">
+      <c r="C8" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" s="48">
         <v>46298</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="27">
-      <c r="A7" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D7" s="19">
-        <v>46298</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D8" s="19">
-        <v>46298</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="5" t="s">
         <v>182</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D9" s="19">
-        <v>46298</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -1586,178 +3016,201 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="7.375" customWidth="1"/>
-    <col min="4" max="4" width="46" customWidth="1"/>
+    <col min="1" max="1" width="42.4375" customWidth="1"/>
+    <col min="2" max="2" width="52.5625" customWidth="1"/>
+    <col min="3" max="3" width="10.9375" customWidth="1"/>
+    <col min="4" max="4" width="52.5625" customWidth="1"/>
+    <col min="5" max="6" width="10.5625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="17.649999999999999">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:6" ht="20" customHeight="1">
+      <c r="A1" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+    </row>
+    <row r="2" spans="1:6" ht="14.25">
+      <c r="A2" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-    </row>
-    <row r="3" spans="1:6" ht="27.75">
-      <c r="A3" s="3" t="s">
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+    </row>
+    <row r="3" spans="1:6" ht="28.5">
+      <c r="A3" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="C3" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="16" t="s">
+        <v>173</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+    </row>
+    <row r="4" spans="1:6" ht="28.5">
+      <c r="A4" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="B4" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="21" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+    </row>
+    <row r="5" spans="1:6" ht="14.25">
+      <c r="A5" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B5" s="19">
+        <v>100.58</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>141</v>
+      </c>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="1:6" ht="14.25">
+      <c r="A6" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D4" t="s">
+      <c r="B6" s="19">
+        <v>0.08</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
+      <c r="D6" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:6" ht="14.25">
+      <c r="A7" s="12" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
+      <c r="B7" s="19">
+        <v>0.04</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="B6" s="5">
-        <v>100.58</v>
-      </c>
-      <c r="C6" t="s">
-        <v>148</v>
-      </c>
-      <c r="D6" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:6" ht="14.25">
+      <c r="A8" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B7" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="B8" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:6" ht="14.25">
+      <c r="A9" s="12" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
+      <c r="B9" s="19">
+        <v>1</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="B8" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="C8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="D9" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:6" ht="14.25">
+      <c r="A10" s="12" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
+      <c r="B10" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6" ht="14.25">
+      <c r="A11" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B9" s="5">
-        <v>0.05</v>
-      </c>
-      <c r="C9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="B11" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="21" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="1:6" ht="14.25">
+      <c r="A12" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B10" s="5">
-        <v>1</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="B12" s="20">
+        <v>0.5</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="D10" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>51</v>
-      </c>
-      <c r="B11" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="C11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
-        <v>52</v>
-      </c>
-      <c r="B12" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="C12" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="C13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" t="s">
-        <v>55</v>
-      </c>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1769,393 +3222,393 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="61.9375" customWidth="1"/>
-    <col min="2" max="2" width="32" customWidth="1"/>
-    <col min="3" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="22" customWidth="1"/>
-    <col min="5" max="5" width="5.9375" customWidth="1"/>
-    <col min="6" max="6" width="23.6875" customWidth="1"/>
-    <col min="7" max="7" width="18.3125" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="20.75" customWidth="1"/>
-    <col min="10" max="10" width="16.3125" customWidth="1"/>
+    <col min="1" max="1" width="10.5625" customWidth="1"/>
+    <col min="2" max="2" width="30.875" customWidth="1"/>
+    <col min="3" max="3" width="26.6875" customWidth="1"/>
+    <col min="4" max="4" width="20.375" customWidth="1"/>
+    <col min="5" max="5" width="10.5625" customWidth="1"/>
+    <col min="6" max="6" width="31.9375" customWidth="1"/>
+    <col min="7" max="7" width="52.5625" customWidth="1"/>
+    <col min="8" max="8" width="21.4375" customWidth="1"/>
+    <col min="9" max="9" width="25.625" customWidth="1"/>
+    <col min="10" max="10" width="20.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.649999999999999">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:10" ht="20" customHeight="1">
+      <c r="A1" s="49" t="s">
+        <v>51</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+    </row>
+    <row r="2" spans="1:10" ht="28.5">
+      <c r="A2" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-    </row>
-    <row r="3" spans="1:10" ht="83.25">
-      <c r="A3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="G2" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="I2" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="J2" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="H3" s="3" t="s">
+    </row>
+    <row r="3" spans="1:10" ht="14.25">
+      <c r="A3" s="22">
+        <v>1</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="C3" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="27">
-      <c r="A4" s="2">
+      <c r="D3" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="F3" s="24">
+        <v>322</v>
+      </c>
+      <c r="G3" s="26">
+        <v>13.2</v>
+      </c>
+      <c r="H3" s="26">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="F4" s="8">
-        <v>322</v>
-      </c>
-      <c r="G4" s="9">
+      <c r="I3" s="26">
+        <v>0.7</v>
+      </c>
+      <c r="J3" s="29">
+        <f t="shared" ref="J3:J12" si="0">F3*H3*I3</f>
+        <v>225.39999999999998</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="14.25">
+      <c r="A4" s="22">
+        <v>2</v>
+      </c>
+      <c r="B4" s="22" t="s">
+        <v>156</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="E4" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="F4" s="24">
+        <v>50</v>
+      </c>
+      <c r="G4" s="26">
         <v>13.2</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="26">
         <v>1</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="26">
         <v>0.7</v>
       </c>
-      <c r="J4" s="10">
-        <f t="shared" ref="J4:J13" si="0">F4*H4*I4</f>
-        <v>225.39999999999998</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="27">
-      <c r="A5" s="2">
-        <v>2</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="F5" s="8">
-        <v>50</v>
-      </c>
-      <c r="G5" s="9">
-        <v>13.2</v>
-      </c>
-      <c r="H5" s="9">
-        <v>1</v>
-      </c>
-      <c r="I5" s="9">
-        <v>0.7</v>
-      </c>
-      <c r="J5" s="10">
+      <c r="J4" s="29">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="27">
-      <c r="A6" s="2">
+    <row r="5" spans="1:10" ht="14.25">
+      <c r="A5" s="22">
         <v>3</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="F6" s="8">
+      <c r="B5" s="22" t="s">
+        <v>157</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="F5" s="24">
         <v>52</v>
       </c>
-      <c r="G6" s="9">
+      <c r="G5" s="26">
         <v>47.6</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H5" s="26">
         <v>1</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I5" s="26">
         <v>0.9</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J5" s="29">
         <f t="shared" si="0"/>
         <v>46.800000000000004</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="27">
-      <c r="A7" s="2">
+    <row r="6" spans="1:10" ht="14.25">
+      <c r="A6" s="22">
         <v>4</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="F7" s="8">
+      <c r="B6" s="22" t="s">
+        <v>160</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="E6" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="F6" s="24">
         <v>140</v>
       </c>
-      <c r="G7" s="9">
+      <c r="G6" s="26">
         <v>29</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H6" s="26">
         <v>0.9</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I6" s="26">
         <v>0.9</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J6" s="29">
         <f t="shared" si="0"/>
         <v>113.4</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="27">
-      <c r="A8" s="2">
+    <row r="7" spans="1:10" ht="14.25">
+      <c r="A7" s="22">
         <v>5</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="F8" s="8">
+      <c r="B7" s="22" t="s">
+        <v>161</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="F7" s="24">
         <v>36</v>
       </c>
-      <c r="G8" s="9">
+      <c r="G7" s="26">
         <v>29</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H7" s="26">
         <v>0.9</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I7" s="26">
         <v>0.9</v>
       </c>
-      <c r="J8" s="10">
+      <c r="J7" s="29">
         <f t="shared" si="0"/>
         <v>29.16</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="27">
-      <c r="A9" s="2">
+    <row r="8" spans="1:10" ht="14.25">
+      <c r="A8" s="22">
         <v>6</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="F9" s="8">
+      <c r="B8" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="F8" s="24">
         <v>1678</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G8" s="26">
         <v>32</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H8" s="26">
         <v>0.8</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I8" s="26">
         <v>0.35</v>
       </c>
-      <c r="J9" s="10">
+      <c r="J8" s="29">
         <f t="shared" si="0"/>
         <v>469.84</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="27">
-      <c r="A10" s="2">
+    <row r="9" spans="1:10" ht="14.25">
+      <c r="A9" s="22">
         <v>7</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="F10" s="8">
+      <c r="B9" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="F9" s="24">
         <v>5815</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G9" s="26">
         <v>32</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H9" s="26">
         <v>0.7</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I9" s="26">
         <v>0.3</v>
       </c>
-      <c r="J10" s="10">
+      <c r="J9" s="29">
         <f t="shared" si="0"/>
         <v>1221.1499999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="27">
-      <c r="A11" s="2">
+    <row r="10" spans="1:10" ht="14.25">
+      <c r="A10" s="22">
         <v>8</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="F11" s="8">
+      <c r="B10" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="F10" s="24">
         <v>372</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G10" s="26">
         <v>13.2</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H10" s="26">
         <v>0.5</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I10" s="26">
         <v>0.25</v>
       </c>
-      <c r="J11" s="10">
+      <c r="J10" s="29">
         <f t="shared" si="0"/>
         <v>46.5</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="27">
-      <c r="A12" s="2">
+    <row r="11" spans="1:10" ht="14.25">
+      <c r="A11" s="22">
         <v>9</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="B11" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="F12" s="8">
+      <c r="C11" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="F11" s="24">
         <v>820</v>
       </c>
-      <c r="G12" s="9">
+      <c r="G11" s="26">
         <v>13.2</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H11" s="26">
         <v>0.5</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I11" s="26">
         <v>0.25</v>
       </c>
-      <c r="J12" s="10">
+      <c r="J11" s="29">
         <f t="shared" si="0"/>
         <v>102.5</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="27">
-      <c r="A13" s="2">
+    <row r="12" spans="1:10" ht="14.25">
+      <c r="A12" s="23">
         <v>10</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="F13" s="8">
+      <c r="B12" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="F12" s="25">
         <v>375</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G12" s="27">
         <v>13.2</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H12" s="27">
         <v>0.5</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I12" s="27">
         <v>0.25</v>
       </c>
-      <c r="J13" s="10">
+      <c r="J12" s="28">
         <f t="shared" si="0"/>
         <v>46.875</v>
       </c>
@@ -2164,7 +3617,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:J1"/>
   </mergeCells>
-  <conditionalFormatting sqref="J4:J13">
+  <conditionalFormatting sqref="J3:J12">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -2173,7 +3626,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J4:J13">
+  <conditionalFormatting sqref="J3:J12">
     <cfRule type="dataBar" priority="2">
       <dataBar>
         <cfvo type="min"/>
@@ -2203,7 +3656,7 @@
               <x14:axisColor auto="1"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>J4:J13</xm:sqref>
+          <xm:sqref>J3:J12</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -2213,307 +3666,353 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="55.3125" customWidth="1"/>
-    <col min="2" max="2" width="19.625" customWidth="1"/>
-    <col min="3" max="3" width="19.375" customWidth="1"/>
-    <col min="4" max="4" width="18.3125" customWidth="1"/>
-    <col min="5" max="5" width="16.4375" customWidth="1"/>
-    <col min="6" max="6" width="16.5625" customWidth="1"/>
-    <col min="7" max="7" width="32" customWidth="1"/>
+    <col min="1" max="1" width="10.9375" customWidth="1"/>
+    <col min="2" max="2" width="15.125" customWidth="1"/>
+    <col min="3" max="3" width="21.4375" customWidth="1"/>
+    <col min="4" max="5" width="25.625" customWidth="1"/>
+    <col min="6" max="6" width="21.4375" customWidth="1"/>
+    <col min="7" max="7" width="52.5625" customWidth="1"/>
+    <col min="8" max="8" width="10.5625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.649999999999999">
-      <c r="A1" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-    </row>
-    <row r="3" spans="1:8" ht="27.75">
-      <c r="A3" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="11">
+    <row r="1" spans="1:8" ht="20" customHeight="1">
+      <c r="A1" s="49" t="s">
+        <v>176</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+    </row>
+    <row r="2" spans="1:8" ht="14.25">
+      <c r="A2" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>145</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="G2" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" ht="28.5">
+      <c r="A3" s="30">
         <v>45931</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B3" s="32">
         <v>26.25</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C3" s="32">
         <v>11.25</v>
       </c>
-      <c r="D4" s="13">
+      <c r="D3" s="32">
         <v>15.5</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E3" s="32">
         <v>13</v>
       </c>
-      <c r="F4" s="14">
-        <f t="shared" ref="F4:F15" si="0">AVERAGE(B4:E4)</f>
+      <c r="F3" s="34">
+        <f t="shared" ref="F3:F14" si="0">AVERAGE(B3:E3)</f>
         <v>16.5</v>
       </c>
-      <c r="G4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="11">
+      <c r="G3" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:8" ht="14.25">
+      <c r="A4" s="30">
         <v>45962</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B4" s="32">
         <v>31.2</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C4" s="32">
         <v>20.2</v>
       </c>
-      <c r="D5" s="13">
+      <c r="D4" s="32">
         <v>30.4</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E4" s="32">
         <v>17</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F4" s="34">
         <f t="shared" si="0"/>
         <v>24.7</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="11">
+      <c r="G4" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" ht="14.25">
+      <c r="A5" s="30">
         <v>45992</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B5" s="32">
         <v>22.25</v>
       </c>
-      <c r="C6" s="13">
+      <c r="C5" s="32">
         <v>13.75</v>
       </c>
-      <c r="D6" s="13">
+      <c r="D5" s="32">
         <v>0</v>
       </c>
-      <c r="E6" s="13">
+      <c r="E5" s="32">
         <v>14.5</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F5" s="34">
         <f t="shared" si="0"/>
         <v>12.625</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="11">
+      <c r="G5" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" ht="14.25">
+      <c r="A6" s="30">
         <v>46023</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B6" s="32">
         <v>26.25</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C6" s="32">
         <v>19.5</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D6" s="32">
         <v>0</v>
       </c>
-      <c r="E7" s="13">
+      <c r="E6" s="32">
         <v>16.5</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F6" s="34">
         <f t="shared" si="0"/>
         <v>15.5625</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="11">
+      <c r="G6" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:8" ht="14.25">
+      <c r="A7" s="30">
         <v>46054</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B7" s="32">
         <v>34</v>
       </c>
-      <c r="C8" s="13">
+      <c r="C7" s="32">
         <v>29.25</v>
       </c>
-      <c r="D8" s="13">
+      <c r="D7" s="32">
         <v>0</v>
       </c>
-      <c r="E8" s="13">
+      <c r="E7" s="32">
         <v>26.75</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F7" s="34">
         <f t="shared" si="0"/>
         <v>22.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="11">
+      <c r="G7" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:8" ht="14.25">
+      <c r="A8" s="30">
         <v>46082</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B8" s="32">
         <v>46</v>
       </c>
-      <c r="C9" s="13">
+      <c r="C8" s="32">
         <v>39</v>
       </c>
-      <c r="D9" s="13">
+      <c r="D8" s="32">
         <v>25.2</v>
       </c>
-      <c r="E9" s="13">
+      <c r="E8" s="32">
         <v>33.6</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F8" s="34">
         <f t="shared" si="0"/>
         <v>35.950000000000003</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="11">
+      <c r="G8" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" ht="14.25">
+      <c r="A9" s="30">
         <v>46113</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B9" s="32">
         <v>61.25</v>
       </c>
-      <c r="C10" s="13">
+      <c r="C9" s="32">
         <v>46.75</v>
       </c>
-      <c r="D10" s="13">
+      <c r="D9" s="32">
         <v>15.75</v>
       </c>
-      <c r="E10" s="13">
+      <c r="E9" s="32">
         <v>46.75</v>
       </c>
-      <c r="F10" s="14">
+      <c r="F9" s="34">
         <f t="shared" si="0"/>
         <v>42.625</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="11">
+      <c r="G9" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="H9" s="1"/>
+    </row>
+    <row r="10" spans="1:8" ht="14.25">
+      <c r="A10" s="30">
         <v>46143</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B10" s="32">
         <v>80.400000000000006</v>
       </c>
-      <c r="C11" s="13">
+      <c r="C10" s="32">
         <v>56.2</v>
       </c>
-      <c r="D11" s="13">
+      <c r="D10" s="32">
         <v>26.8</v>
       </c>
-      <c r="E11" s="13">
+      <c r="E10" s="32">
         <v>61.8</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F10" s="34">
         <f t="shared" si="0"/>
         <v>56.300000000000011</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="11">
+      <c r="G10" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="H10" s="1"/>
+    </row>
+    <row r="11" spans="1:8" ht="14.25">
+      <c r="A11" s="30">
         <v>46174</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B11" s="32">
         <v>74</v>
       </c>
-      <c r="C12" s="13">
+      <c r="C11" s="32">
         <v>44.75</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D11" s="32">
         <v>36</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E11" s="32">
         <v>44.75</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F11" s="34">
         <f t="shared" si="0"/>
         <v>49.875</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="11">
+      <c r="G11" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="H11" s="1"/>
+    </row>
+    <row r="12" spans="1:8" ht="14.25">
+      <c r="A12" s="30">
         <v>46204</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B12" s="32">
         <v>55</v>
       </c>
-      <c r="C13" s="13">
+      <c r="C12" s="32">
         <v>36.5</v>
       </c>
-      <c r="D13" s="13">
+      <c r="D12" s="32">
         <v>0</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E12" s="32">
         <v>23.75</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F12" s="34">
         <f t="shared" si="0"/>
         <v>28.8125</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="11">
+      <c r="G12" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="H12" s="1"/>
+    </row>
+    <row r="13" spans="1:8" ht="14.25">
+      <c r="A13" s="30">
         <v>46235</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B13" s="32">
         <v>54</v>
       </c>
-      <c r="C14" s="13">
+      <c r="C13" s="32">
         <v>25.8</v>
       </c>
-      <c r="D14" s="13">
+      <c r="D13" s="32">
         <v>0</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E13" s="32">
         <v>19.8</v>
       </c>
-      <c r="F14" s="14">
+      <c r="F13" s="34">
         <f t="shared" si="0"/>
         <v>24.9</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="11">
+      <c r="G13" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="H13" s="1"/>
+    </row>
+    <row r="14" spans="1:8" ht="14.25">
+      <c r="A14" s="31">
         <v>46266</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B14" s="33">
         <v>60</v>
       </c>
-      <c r="C15" s="13">
+      <c r="C14" s="33">
         <v>41</v>
       </c>
-      <c r="D15" s="13">
+      <c r="D14" s="33">
         <v>8.33</v>
       </c>
-      <c r="E15" s="13">
+      <c r="E14" s="33">
         <v>30.33</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F14" s="35">
         <f t="shared" si="0"/>
         <v>34.914999999999999</v>
       </c>
+      <c r="G14" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="H14" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2528,389 +4027,389 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="51.9375" customWidth="1"/>
-    <col min="2" max="2" width="20.4375" customWidth="1"/>
-    <col min="3" max="3" width="18.8125" customWidth="1"/>
-    <col min="4" max="4" width="24.25" customWidth="1"/>
-    <col min="5" max="5" width="17.375" customWidth="1"/>
-    <col min="6" max="6" width="20.3125" customWidth="1"/>
-    <col min="7" max="7" width="25" customWidth="1"/>
-    <col min="8" max="8" width="21" customWidth="1"/>
+    <col min="1" max="1" width="10.9375" customWidth="1"/>
+    <col min="2" max="2" width="36.125" customWidth="1"/>
+    <col min="3" max="3" width="31.9375" customWidth="1"/>
+    <col min="4" max="4" width="18.25" customWidth="1"/>
+    <col min="5" max="5" width="19.3125" customWidth="1"/>
+    <col min="6" max="6" width="25.625" customWidth="1"/>
+    <col min="7" max="7" width="52.5625" customWidth="1"/>
+    <col min="8" max="8" width="26.6875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.649999999999999">
-      <c r="A1" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-    </row>
-    <row r="3" spans="1:8" ht="55.5">
-      <c r="A3" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="11">
+    <row r="1" spans="1:8" ht="20" customHeight="1">
+      <c r="A1" s="49" t="s">
+        <v>178</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+    </row>
+    <row r="2" spans="1:8" ht="28.5">
+      <c r="A2" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="14.25">
+      <c r="A3" s="30">
         <v>45931</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B3" s="24">
         <v>185</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C3" s="24">
         <v>9821</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D3" s="24">
         <v>2339</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E3" s="24">
         <v>521</v>
       </c>
-      <c r="F4" s="15">
-        <f t="shared" ref="F4:F15" si="0">SUM(B4:E4)</f>
+      <c r="F3" s="36">
+        <f t="shared" ref="F3:F14" si="0">SUM(B3:E3)</f>
         <v>12866</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G3" s="19">
         <v>0.109</v>
       </c>
-      <c r="H4" s="15">
-        <f t="shared" ref="H4:H15" si="1">F4*G4</f>
+      <c r="H3" s="39">
+        <f t="shared" ref="H3:H14" si="1">F3*G3</f>
         <v>1402.394</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="11">
+    <row r="4" spans="1:8" ht="14.25">
+      <c r="A4" s="30">
         <v>45962</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B4" s="24">
         <v>204</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C4" s="24">
         <v>10493</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D4" s="24">
         <v>2076</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E4" s="24">
         <v>478</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F4" s="36">
         <f t="shared" si="0"/>
         <v>13251</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G4" s="19">
         <v>0.109</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H4" s="39">
         <f t="shared" si="1"/>
         <v>1444.3589999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="11">
+    <row r="5" spans="1:8" ht="14.25">
+      <c r="A5" s="30">
         <v>45992</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B5" s="24">
         <v>198</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C5" s="24">
         <v>11113</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D5" s="24">
         <v>2135</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E5" s="24">
         <v>483</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F5" s="36">
         <f t="shared" si="0"/>
         <v>13929</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G5" s="19">
         <v>0.109</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H5" s="39">
         <f t="shared" si="1"/>
         <v>1518.261</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="11">
+    <row r="6" spans="1:8" ht="14.25">
+      <c r="A6" s="30">
         <v>46023</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B6" s="24">
         <v>120</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C6" s="24">
         <v>6392</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D6" s="24">
         <v>1487</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E6" s="24">
         <v>356</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F6" s="36">
         <f t="shared" si="0"/>
         <v>8355</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G6" s="19">
         <v>0.109</v>
       </c>
-      <c r="H7" s="15">
+      <c r="H6" s="39">
         <f t="shared" si="1"/>
         <v>910.69500000000005</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="11">
+    <row r="7" spans="1:8" ht="14.25">
+      <c r="A7" s="30">
         <v>46054</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B7" s="24">
         <v>122</v>
       </c>
-      <c r="C8" s="6">
+      <c r="C7" s="24">
         <v>6746</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D7" s="24">
         <v>1470</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E7" s="24">
         <v>380</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F7" s="36">
         <f t="shared" si="0"/>
         <v>8718</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G7" s="19">
         <v>0.109</v>
       </c>
-      <c r="H8" s="15">
+      <c r="H7" s="39">
         <f t="shared" si="1"/>
         <v>950.26199999999994</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="11">
+    <row r="8" spans="1:8" ht="14.25">
+      <c r="A8" s="30">
         <v>46082</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B8" s="24">
         <v>144</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C8" s="24">
         <v>7499</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D8" s="24">
         <v>1928</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E8" s="24">
         <v>417</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F8" s="36">
         <f t="shared" si="0"/>
         <v>9988</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G8" s="19">
         <v>0.109</v>
       </c>
-      <c r="H9" s="15">
+      <c r="H8" s="39">
         <f t="shared" si="1"/>
         <v>1088.692</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="11">
+    <row r="9" spans="1:8" ht="14.25">
+      <c r="A9" s="30">
         <v>46113</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B9" s="24">
         <v>147</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C9" s="24">
         <v>8997</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D9" s="24">
         <v>1882</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E9" s="24">
         <v>405</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F9" s="36">
         <f t="shared" si="0"/>
         <v>11431</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G9" s="19">
         <v>0.109</v>
       </c>
-      <c r="H10" s="15">
+      <c r="H9" s="39">
         <f t="shared" si="1"/>
         <v>1245.979</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="11">
+    <row r="10" spans="1:8" ht="14.25">
+      <c r="A10" s="30">
         <v>46143</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B10" s="24">
         <v>137</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C10" s="24">
         <v>7534</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D10" s="24">
         <v>2022</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E10" s="24">
         <v>294</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F10" s="36">
         <f t="shared" si="0"/>
         <v>9987</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G10" s="19">
         <v>0.109</v>
       </c>
-      <c r="H11" s="15">
+      <c r="H10" s="39">
         <f t="shared" si="1"/>
         <v>1088.5830000000001</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="11">
+    <row r="11" spans="1:8" ht="14.25">
+      <c r="A11" s="30">
         <v>46174</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B11" s="24">
         <v>133</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C11" s="24">
         <v>7263</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D11" s="24">
         <v>1930</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E11" s="24">
         <v>348</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F11" s="36">
         <f t="shared" si="0"/>
         <v>9674</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G11" s="19">
         <v>0.109</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H11" s="39">
         <f t="shared" si="1"/>
         <v>1054.4659999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="11">
+    <row r="12" spans="1:8" ht="14.25">
+      <c r="A12" s="30">
         <v>46204</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B12" s="24">
         <v>104</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C12" s="24">
         <v>4388</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D12" s="24">
         <v>1325</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E12" s="24">
         <v>270</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F12" s="36">
         <f t="shared" si="0"/>
         <v>6087</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G12" s="19">
         <v>0.109</v>
       </c>
-      <c r="H13" s="15">
+      <c r="H12" s="39">
         <f t="shared" si="1"/>
         <v>663.48299999999995</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="11">
+    <row r="13" spans="1:8" ht="14.25">
+      <c r="A13" s="30">
         <v>46235</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B13" s="24">
         <v>94</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C13" s="24">
         <v>3706</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D13" s="24">
         <v>1127</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E13" s="24">
         <v>219</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F13" s="36">
         <f t="shared" si="0"/>
         <v>5146</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G13" s="19">
         <v>0.109</v>
       </c>
-      <c r="H14" s="15">
+      <c r="H13" s="39">
         <f t="shared" si="1"/>
         <v>560.91399999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="11">
+    <row r="14" spans="1:8" ht="14.25">
+      <c r="A14" s="31">
         <v>46266</v>
       </c>
-      <c r="B15" s="6">
+      <c r="B14" s="25">
         <v>110.33333333333333</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C14" s="25">
         <v>5965</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D14" s="25">
         <v>1627</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E14" s="25">
         <v>298</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F14" s="37">
         <f t="shared" si="0"/>
         <v>8000.333333333333</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G14" s="20">
         <v>0.109</v>
       </c>
-      <c r="H15" s="15">
+      <c r="H14" s="38">
         <f t="shared" si="1"/>
         <v>872.03633333333335</v>
       </c>
@@ -2928,433 +4427,457 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="66.75" customWidth="1"/>
-    <col min="2" max="2" width="16.5625" customWidth="1"/>
-    <col min="3" max="3" width="17.25" customWidth="1"/>
-    <col min="4" max="4" width="24.0625" customWidth="1"/>
-    <col min="5" max="5" width="17.625" customWidth="1"/>
-    <col min="6" max="6" width="20.4375" customWidth="1"/>
-    <col min="7" max="7" width="12.9375" customWidth="1"/>
-    <col min="8" max="8" width="30" customWidth="1"/>
+    <col min="1" max="1" width="10.9375" customWidth="1"/>
+    <col min="2" max="2" width="21.4375" customWidth="1"/>
+    <col min="3" max="3" width="20.375" customWidth="1"/>
+    <col min="4" max="4" width="29.8125" customWidth="1"/>
+    <col min="5" max="5" width="20.375" customWidth="1"/>
+    <col min="6" max="6" width="25.625" customWidth="1"/>
+    <col min="7" max="7" width="17.1875" customWidth="1"/>
+    <col min="8" max="8" width="15.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.649999999999999">
-      <c r="A1" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-    </row>
-    <row r="3" spans="1:8" ht="27.75">
-      <c r="A3" s="3" t="s">
+    <row r="1" spans="1:8" ht="20" customHeight="1">
+      <c r="A1" s="49" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+    </row>
+    <row r="2" spans="1:8" ht="14.25">
+      <c r="A2" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="E2" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="11">
+      <c r="F2" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="14.25">
+      <c r="A3" s="30">
+        <f>'03_Google_Trends'!A3</f>
+        <v>45931</v>
+      </c>
+      <c r="B3" s="40">
+        <f>'03_Google_Trends'!F3</f>
+        <v>16.5</v>
+      </c>
+      <c r="C3" s="40">
+        <f t="shared" ref="C3:C14" si="0">IF(MAX($B$3:$B$14)=0,0,B3/MAX($B$3:$B$14)*100)</f>
+        <v>29.307282415630542</v>
+      </c>
+      <c r="D3" s="42">
+        <f>'04_Wordstat'!H3</f>
+        <v>1402.394</v>
+      </c>
+      <c r="E3" s="40">
+        <f t="shared" ref="E3:E14" si="1">IF(MAX($D$3:$D$14)=0,0,D3/MAX($D$3:$D$14)*100)</f>
+        <v>92.368439945437572</v>
+      </c>
+      <c r="F3" s="34">
+        <f>C3*'01_Параметры'!$B$10+E3*'01_Параметры'!$B$11</f>
+        <v>60.837861180534055</v>
+      </c>
+      <c r="G3" s="9" t="str">
+        <f t="shared" ref="G3:G14" si="2">IF(F3&gt;=75,"высокий",IF(F3&gt;=45,"средний","низкий"))</f>
+        <v>средний</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="14.25">
+      <c r="A4" s="30">
         <f>'03_Google_Trends'!A4</f>
-        <v>45931</v>
-      </c>
-      <c r="B4" s="12">
+        <v>45962</v>
+      </c>
+      <c r="B4" s="40">
         <f>'03_Google_Trends'!F4</f>
-        <v>16.5</v>
-      </c>
-      <c r="C4" s="12">
-        <f t="shared" ref="C4:C15" si="0">IF(MAX($B$4:$B$15)=0,0,B4/MAX($B$4:$B$15)*100)</f>
-        <v>29.307282415630542</v>
-      </c>
-      <c r="D4" s="7">
-        <f>'04_Wordstat'!H4</f>
-        <v>1402.394</v>
-      </c>
-      <c r="E4" s="12">
-        <f t="shared" ref="E4:E15" si="1">IF(MAX($D$4:$D$15)=0,0,D4/MAX($D$4:$D$15)*100)</f>
-        <v>92.368439945437572</v>
-      </c>
-      <c r="F4" s="14">
-        <f>C4*'01_Параметры'!$B$11+E4*'01_Параметры'!$B$12</f>
-        <v>60.837861180534055</v>
-      </c>
-      <c r="G4" t="str">
-        <f t="shared" ref="G4:G15" si="2">IF(F4&gt;=75,"высокий",IF(F4&gt;=45,"средний","низкий"))</f>
-        <v>средний</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="11">
-        <f>'03_Google_Trends'!A5</f>
-        <v>45962</v>
-      </c>
-      <c r="B5" s="12">
-        <f>'03_Google_Trends'!F5</f>
         <v>24.7</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C4" s="40">
         <f t="shared" si="0"/>
         <v>43.872113676731786</v>
       </c>
-      <c r="D5" s="7">
-        <f>'04_Wordstat'!H5</f>
+      <c r="D4" s="42">
+        <f>'04_Wordstat'!H4</f>
         <v>1444.3589999999999</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E4" s="40">
         <f t="shared" si="1"/>
         <v>95.132457462847299</v>
       </c>
-      <c r="F5" s="14">
-        <f>C5*'01_Параметры'!$B$11+E5*'01_Параметры'!$B$12</f>
+      <c r="F4" s="34">
+        <f>C4*'01_Параметры'!$B$10+E4*'01_Параметры'!$B$11</f>
         <v>69.502285569789535</v>
       </c>
-      <c r="G5" t="str">
+      <c r="G4" s="9" t="str">
         <f t="shared" si="2"/>
         <v>средний</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="11">
-        <f>'03_Google_Trends'!A6</f>
+      <c r="H4" s="16" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="14.25">
+      <c r="A5" s="30">
+        <f>'03_Google_Trends'!A5</f>
         <v>45992</v>
       </c>
-      <c r="B6" s="12">
-        <f>'03_Google_Trends'!F6</f>
+      <c r="B5" s="40">
+        <f>'03_Google_Trends'!F5</f>
         <v>12.625</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C5" s="40">
         <f t="shared" si="0"/>
         <v>22.424511545293068</v>
       </c>
-      <c r="D6" s="7">
-        <f>'04_Wordstat'!H6</f>
+      <c r="D5" s="42">
+        <f>'04_Wordstat'!H5</f>
         <v>1518.261</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E5" s="40">
         <f t="shared" si="1"/>
         <v>100</v>
       </c>
-      <c r="F6" s="14">
-        <f>C6*'01_Параметры'!$B$11+E6*'01_Параметры'!$B$12</f>
+      <c r="F5" s="34">
+        <f>C5*'01_Параметры'!$B$10+E5*'01_Параметры'!$B$11</f>
         <v>61.212255772646536</v>
       </c>
-      <c r="G6" t="str">
+      <c r="G5" s="9" t="str">
         <f t="shared" si="2"/>
         <v>средний</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="11">
-        <f>'03_Google_Trends'!A7</f>
+      <c r="H5" s="16" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="14.25">
+      <c r="A6" s="30">
+        <f>'03_Google_Trends'!A6</f>
         <v>46023</v>
       </c>
-      <c r="B7" s="12">
-        <f>'03_Google_Trends'!F7</f>
+      <c r="B6" s="40">
+        <f>'03_Google_Trends'!F6</f>
         <v>15.5625</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C6" s="40">
         <f t="shared" si="0"/>
         <v>27.642095914742448</v>
       </c>
-      <c r="D7" s="7">
-        <f>'04_Wordstat'!H7</f>
+      <c r="D6" s="42">
+        <f>'04_Wordstat'!H6</f>
         <v>910.69500000000005</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E6" s="40">
         <f t="shared" si="1"/>
         <v>59.982769760930431</v>
       </c>
-      <c r="F7" s="14">
-        <f>C7*'01_Параметры'!$B$11+E7*'01_Параметры'!$B$12</f>
+      <c r="F6" s="34">
+        <f>C6*'01_Параметры'!$B$10+E6*'01_Параметры'!$B$11</f>
         <v>43.81243283783644</v>
       </c>
-      <c r="G7" t="str">
+      <c r="G6" s="9" t="str">
         <f t="shared" si="2"/>
         <v>низкий</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="11">
-        <f>'03_Google_Trends'!A8</f>
+      <c r="H6" s="16" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="14.25">
+      <c r="A7" s="30">
+        <f>'03_Google_Trends'!A7</f>
         <v>46054</v>
       </c>
-      <c r="B8" s="12">
-        <f>'03_Google_Trends'!F8</f>
+      <c r="B7" s="40">
+        <f>'03_Google_Trends'!F7</f>
         <v>22.5</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C7" s="40">
         <f t="shared" si="0"/>
         <v>39.964476021314375</v>
       </c>
-      <c r="D8" s="7">
-        <f>'04_Wordstat'!H8</f>
+      <c r="D7" s="42">
+        <f>'04_Wordstat'!H7</f>
         <v>950.26199999999994</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E7" s="40">
         <f t="shared" si="1"/>
         <v>62.588843420202458</v>
       </c>
-      <c r="F8" s="14">
-        <f>C8*'01_Параметры'!$B$11+E8*'01_Параметры'!$B$12</f>
+      <c r="F7" s="34">
+        <f>C7*'01_Параметры'!$B$10+E7*'01_Параметры'!$B$11</f>
         <v>51.276659720758417</v>
       </c>
-      <c r="G8" t="str">
+      <c r="G7" s="9" t="str">
         <f t="shared" si="2"/>
         <v>средний</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="11">
-        <f>'03_Google_Trends'!A9</f>
+      <c r="H7" s="16" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="14.25">
+      <c r="A8" s="30">
+        <f>'03_Google_Trends'!A8</f>
         <v>46082</v>
       </c>
-      <c r="B9" s="12">
-        <f>'03_Google_Trends'!F9</f>
+      <c r="B8" s="40">
+        <f>'03_Google_Trends'!F8</f>
         <v>35.950000000000003</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C8" s="40">
         <f t="shared" si="0"/>
         <v>63.854351687388977</v>
       </c>
-      <c r="D9" s="7">
-        <f>'04_Wordstat'!H9</f>
+      <c r="D8" s="42">
+        <f>'04_Wordstat'!H8</f>
         <v>1088.692</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E8" s="40">
         <f t="shared" si="1"/>
         <v>71.70651159451505</v>
       </c>
-      <c r="F9" s="14">
-        <f>C9*'01_Параметры'!$B$11+E9*'01_Параметры'!$B$12</f>
+      <c r="F8" s="34">
+        <f>C8*'01_Параметры'!$B$10+E8*'01_Параметры'!$B$11</f>
         <v>67.780431640952017</v>
       </c>
-      <c r="G9" t="str">
+      <c r="G8" s="9" t="str">
         <f t="shared" si="2"/>
         <v>средний</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="11">
-        <f>'03_Google_Trends'!A10</f>
+      <c r="H8" s="16" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="14.25">
+      <c r="A9" s="30">
+        <f>'03_Google_Trends'!A9</f>
         <v>46113</v>
       </c>
-      <c r="B10" s="12">
-        <f>'03_Google_Trends'!F10</f>
+      <c r="B9" s="40">
+        <f>'03_Google_Trends'!F9</f>
         <v>42.625</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C9" s="40">
         <f t="shared" si="0"/>
         <v>75.710479573712234</v>
       </c>
-      <c r="D10" s="7">
-        <f>'04_Wordstat'!H10</f>
+      <c r="D9" s="42">
+        <f>'04_Wordstat'!H9</f>
         <v>1245.979</v>
       </c>
-      <c r="E10" s="12">
+      <c r="E9" s="40">
         <f t="shared" si="1"/>
         <v>82.066192835092252</v>
       </c>
-      <c r="F10" s="14">
-        <f>C10*'01_Параметры'!$B$11+E10*'01_Параметры'!$B$12</f>
+      <c r="F9" s="34">
+        <f>C9*'01_Параметры'!$B$10+E9*'01_Параметры'!$B$11</f>
         <v>78.888336204402236</v>
       </c>
-      <c r="G10" t="str">
+      <c r="G9" s="9" t="str">
         <f t="shared" si="2"/>
         <v>высокий</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="11">
-        <f>'03_Google_Trends'!A11</f>
+      <c r="H9" s="16" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="14.25">
+      <c r="A10" s="30">
+        <f>'03_Google_Trends'!A10</f>
         <v>46143</v>
       </c>
-      <c r="B11" s="12">
-        <f>'03_Google_Trends'!F11</f>
+      <c r="B10" s="40">
+        <f>'03_Google_Trends'!F10</f>
         <v>56.300000000000011</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C10" s="40">
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="D11" s="7">
-        <f>'04_Wordstat'!H11</f>
+      <c r="D10" s="42">
+        <f>'04_Wordstat'!H10</f>
         <v>1088.5830000000001</v>
       </c>
-      <c r="E11" s="12">
+      <c r="E10" s="40">
         <f t="shared" si="1"/>
         <v>71.699332328236068</v>
       </c>
-      <c r="F11" s="14">
-        <f>C11*'01_Параметры'!$B$11+E11*'01_Параметры'!$B$12</f>
+      <c r="F10" s="34">
+        <f>C10*'01_Параметры'!$B$10+E10*'01_Параметры'!$B$11</f>
         <v>85.849666164118034</v>
       </c>
-      <c r="G11" t="str">
+      <c r="G10" s="9" t="str">
         <f t="shared" si="2"/>
         <v>высокий</v>
       </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="11">
-        <f>'03_Google_Trends'!A12</f>
+      <c r="H10" s="16" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="14.25">
+      <c r="A11" s="30">
+        <f>'03_Google_Trends'!A11</f>
         <v>46174</v>
       </c>
-      <c r="B12" s="12">
-        <f>'03_Google_Trends'!F12</f>
+      <c r="B11" s="40">
+        <f>'03_Google_Trends'!F11</f>
         <v>49.875</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C11" s="40">
         <f t="shared" si="0"/>
         <v>88.587921847246875</v>
       </c>
-      <c r="D12" s="7">
-        <f>'04_Wordstat'!H12</f>
+      <c r="D11" s="42">
+        <f>'04_Wordstat'!H11</f>
         <v>1054.4659999999999</v>
       </c>
-      <c r="E12" s="12">
+      <c r="E11" s="40">
         <f t="shared" si="1"/>
         <v>69.452221982913343</v>
       </c>
-      <c r="F12" s="14">
-        <f>C12*'01_Параметры'!$B$11+E12*'01_Параметры'!$B$12</f>
+      <c r="F11" s="34">
+        <f>C11*'01_Параметры'!$B$10+E11*'01_Параметры'!$B$11</f>
         <v>79.020071915080109</v>
       </c>
-      <c r="G12" t="str">
+      <c r="G11" s="9" t="str">
         <f t="shared" si="2"/>
         <v>высокий</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="11">
-        <f>'03_Google_Trends'!A13</f>
+      <c r="H11" s="16" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="14.25">
+      <c r="A12" s="30">
+        <f>'03_Google_Trends'!A12</f>
         <v>46204</v>
       </c>
-      <c r="B13" s="12">
-        <f>'03_Google_Trends'!F13</f>
+      <c r="B12" s="40">
+        <f>'03_Google_Trends'!F12</f>
         <v>28.8125</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C12" s="40">
         <f t="shared" si="0"/>
         <v>51.176731793960919</v>
       </c>
-      <c r="D13" s="7">
-        <f>'04_Wordstat'!H13</f>
+      <c r="D12" s="42">
+        <f>'04_Wordstat'!H12</f>
         <v>663.48299999999995</v>
       </c>
-      <c r="E13" s="12">
+      <c r="E12" s="40">
         <f t="shared" si="1"/>
         <v>43.700193840189527</v>
       </c>
-      <c r="F13" s="14">
-        <f>C13*'01_Параметры'!$B$11+E13*'01_Параметры'!$B$12</f>
+      <c r="F12" s="34">
+        <f>C12*'01_Параметры'!$B$10+E12*'01_Параметры'!$B$11</f>
         <v>47.438462817075219</v>
       </c>
-      <c r="G13" t="str">
+      <c r="G12" s="9" t="str">
         <f t="shared" si="2"/>
         <v>средний</v>
       </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="11">
-        <f>'03_Google_Trends'!A14</f>
+      <c r="H12" s="16" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="14.25">
+      <c r="A13" s="30">
+        <f>'03_Google_Trends'!A13</f>
         <v>46235</v>
       </c>
-      <c r="B14" s="12">
-        <f>'03_Google_Trends'!F14</f>
+      <c r="B13" s="40">
+        <f>'03_Google_Trends'!F13</f>
         <v>24.9</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C13" s="40">
         <f t="shared" si="0"/>
         <v>44.22735346358791</v>
       </c>
-      <c r="D14" s="7">
-        <f>'04_Wordstat'!H14</f>
+      <c r="D13" s="42">
+        <f>'04_Wordstat'!H13</f>
         <v>560.91399999999999</v>
       </c>
-      <c r="E14" s="12">
+      <c r="E13" s="40">
         <f t="shared" si="1"/>
         <v>36.944504271663433</v>
       </c>
-      <c r="F14" s="14">
-        <f>C14*'01_Параметры'!$B$11+E14*'01_Параметры'!$B$12</f>
+      <c r="F13" s="34">
+        <f>C13*'01_Параметры'!$B$10+E13*'01_Параметры'!$B$11</f>
         <v>40.585928867625668</v>
       </c>
-      <c r="G14" t="str">
+      <c r="G13" s="9" t="str">
         <f t="shared" si="2"/>
         <v>низкий</v>
       </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="11">
-        <f>'03_Google_Trends'!A15</f>
+      <c r="H13" s="16" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="14.25">
+      <c r="A14" s="31">
+        <f>'03_Google_Trends'!A14</f>
         <v>46266</v>
       </c>
-      <c r="B15" s="12">
-        <f>'03_Google_Trends'!F15</f>
+      <c r="B14" s="41">
+        <f>'03_Google_Trends'!F14</f>
         <v>34.914999999999999</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C14" s="41">
         <f t="shared" si="0"/>
         <v>62.015985790408514</v>
       </c>
-      <c r="D15" s="7">
-        <f>'04_Wordstat'!H15</f>
+      <c r="D14" s="43">
+        <f>'04_Wordstat'!H14</f>
         <v>872.03633333333335</v>
       </c>
-      <c r="E15" s="12">
+      <c r="E14" s="41">
         <f t="shared" si="1"/>
         <v>57.436523320649968</v>
       </c>
-      <c r="F15" s="14">
-        <f>C15*'01_Параметры'!$B$11+E15*'01_Параметры'!$B$12</f>
+      <c r="F14" s="35">
+        <f>C14*'01_Параметры'!$B$10+E14*'01_Параметры'!$B$11</f>
         <v>59.726254555529238</v>
       </c>
-      <c r="G15" t="str">
+      <c r="G14" s="10" t="str">
         <f t="shared" si="2"/>
         <v>средний</v>
+      </c>
+      <c r="H14" s="11" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="F4:F15">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFFCE4D6"/>
-        <color rgb="FFFFF2CC"/>
-        <color rgb="FFE2F0D9"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
@@ -3364,251 +4887,312 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="11.0625" customWidth="1"/>
-    <col min="3" max="3" width="7.375" customWidth="1"/>
-    <col min="4" max="4" width="13.875" customWidth="1"/>
-    <col min="5" max="5" width="42" customWidth="1"/>
+    <col min="1" max="1" width="38.1875" customWidth="1"/>
+    <col min="2" max="2" width="14.0625" customWidth="1"/>
+    <col min="3" max="3" width="10.9375" customWidth="1"/>
+    <col min="4" max="4" width="17.1875" customWidth="1"/>
+    <col min="5" max="5" width="52.5625" customWidth="1"/>
+    <col min="6" max="10" width="10.5625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="17.649999999999999">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:10" ht="20" customHeight="1">
+      <c r="A1" s="49" t="s">
+        <v>179</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+      <c r="I1" s="50"/>
+      <c r="J1" s="50"/>
+    </row>
+    <row r="2" spans="1:10" ht="14.25">
+      <c r="A2" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+    </row>
+    <row r="3" spans="1:10" ht="14.25">
+      <c r="A3" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="36">
+        <f>AVERAGE('04_Wordstat'!$H$3:$H$14)</f>
+        <v>1066.6770277777778</v>
+      </c>
+      <c r="C3" s="36">
+        <f>AVERAGE('04_Wordstat'!$H$3:$H$14)</f>
+        <v>1066.6770277777778</v>
+      </c>
+      <c r="D3" s="36">
+        <f>AVERAGE('04_Wordstat'!$H$3:$H$14)</f>
+        <v>1066.6770277777778</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+    </row>
+    <row r="4" spans="1:10" ht="14.25">
+      <c r="A4" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B4" s="19">
+        <v>0.04</v>
+      </c>
+      <c r="C4" s="19">
+        <v>0.08</v>
+      </c>
+      <c r="D4" s="19">
+        <v>0.12</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="1:10" ht="14.25">
+      <c r="A5" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-    </row>
-    <row r="3" spans="1:10" ht="27.75">
-      <c r="A3" s="3" t="s">
+      <c r="B5" s="36">
+        <f>B3*B4</f>
+        <v>42.667081111111109</v>
+      </c>
+      <c r="C5" s="36">
+        <f>C3*C4</f>
+        <v>85.334162222222218</v>
+      </c>
+      <c r="D5" s="36">
+        <f>D3*D4</f>
+        <v>128.00124333333332</v>
+      </c>
+      <c r="E5" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="1:10" ht="14.25">
+      <c r="A6" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="19">
+        <v>0.02</v>
+      </c>
+      <c r="C6" s="19">
+        <v>0.04</v>
+      </c>
+      <c r="D6" s="19">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="E6" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="1:10" ht="14.25">
+      <c r="A7" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="B7" s="36">
+        <f>B5*B6</f>
+        <v>0.85334162222222221</v>
+      </c>
+      <c r="C7" s="36">
+        <f>C5*C6</f>
+        <v>3.4133664888888888</v>
+      </c>
+      <c r="D7" s="36">
+        <f>D5*D6</f>
+        <v>8.960087033333334</v>
+      </c>
+      <c r="E7" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="1:10" ht="14.25">
+      <c r="A8" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="19">
+        <v>0.03</v>
+      </c>
+      <c r="C8" s="19">
+        <v>0.05</v>
+      </c>
+      <c r="D8" s="19">
+        <v>0.08</v>
+      </c>
+      <c r="E8" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="B4" s="15">
-        <f>AVERAGE('04_Wordstat'!$H$4:$H$15)</f>
-        <v>1066.6770277777778</v>
-      </c>
-      <c r="C4" s="15">
-        <f>AVERAGE('04_Wordstat'!$H$4:$H$15)</f>
-        <v>1066.6770277777778</v>
-      </c>
-      <c r="D4" s="15">
-        <f>AVERAGE('04_Wordstat'!$H$4:$H$15)</f>
-        <v>1066.6770277777778</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="1:10" ht="14.25">
+      <c r="A9" s="12" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="C5" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="D5" s="5">
-        <v>0.12</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="B9" s="34">
+        <f>B7*B8</f>
+        <v>2.5600248666666665E-2</v>
+      </c>
+      <c r="C9" s="34">
+        <f>C7*C8</f>
+        <v>0.17066832444444446</v>
+      </c>
+      <c r="D9" s="34">
+        <f>D7*D8</f>
+        <v>0.71680696266666677</v>
+      </c>
+      <c r="E9" s="21" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" t="s">
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="1:10" ht="14.25">
+      <c r="A10" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" s="24">
+        <v>53.88</v>
+      </c>
+      <c r="C10" s="24">
+        <v>100.58</v>
+      </c>
+      <c r="D10" s="24">
+        <v>149.15</v>
+      </c>
+      <c r="E10" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="15">
-        <f>B4*B5</f>
-        <v>42.667081111111109</v>
-      </c>
-      <c r="C6" s="15">
-        <f>C4*C5</f>
-        <v>85.334162222222218</v>
-      </c>
-      <c r="D6" s="15">
-        <f>D4*D5</f>
-        <v>128.00124333333332</v>
-      </c>
-      <c r="E6" t="s">
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="1:10" ht="14.25">
+      <c r="A11" s="12" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7" s="5">
-        <v>0.02</v>
-      </c>
-      <c r="C7" s="5">
-        <v>0.04</v>
-      </c>
-      <c r="D7" s="5">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="B11" s="24">
+        <v>1</v>
+      </c>
+      <c r="C11" s="24">
+        <v>1</v>
+      </c>
+      <c r="D11" s="24">
+        <v>1</v>
+      </c>
+      <c r="E11" s="21" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" t="s">
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="1:10" ht="14.25">
+      <c r="A12" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="15">
-        <f>B6*B7</f>
-        <v>0.85334162222222221</v>
-      </c>
-      <c r="C8" s="15">
-        <f>C6*C7</f>
-        <v>3.4133664888888888</v>
-      </c>
-      <c r="D8" s="15">
-        <f>D6*D7</f>
-        <v>8.960087033333334</v>
-      </c>
-      <c r="E8" t="s">
+      <c r="B12" s="36">
+        <f>B9*B10*B11</f>
+        <v>1.37934139816</v>
+      </c>
+      <c r="C12" s="36">
+        <f>C9*C10*C11</f>
+        <v>17.165820072622225</v>
+      </c>
+      <c r="D12" s="36">
+        <f>D9*D10*D11</f>
+        <v>106.91175848173336</v>
+      </c>
+      <c r="E12" s="21" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="C9" s="5">
-        <v>0.05</v>
-      </c>
-      <c r="D9" s="5">
-        <v>0.08</v>
-      </c>
-      <c r="E9" t="s">
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="1:10" ht="14.25">
+      <c r="A13" s="13" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" t="s">
+      <c r="B13" s="37">
+        <f>B12*12</f>
+        <v>16.552096777919999</v>
+      </c>
+      <c r="C13" s="37">
+        <f>C12*12</f>
+        <v>205.9898408714667</v>
+      </c>
+      <c r="D13" s="37">
+        <f>D12*12</f>
+        <v>1282.9411017808002</v>
+      </c>
+      <c r="E13" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="B10" s="14">
-        <f>B8*B9</f>
-        <v>2.5600248666666665E-2</v>
-      </c>
-      <c r="C10" s="14">
-        <f>C8*C9</f>
-        <v>0.17066832444444446</v>
-      </c>
-      <c r="D10" s="14">
-        <f>D8*D9</f>
-        <v>0.71680696266666677</v>
-      </c>
-      <c r="E10" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B11" s="6">
-        <v>53.88</v>
-      </c>
-      <c r="C11" s="6">
-        <v>100.58</v>
-      </c>
-      <c r="D11" s="6">
-        <v>149.15</v>
-      </c>
-      <c r="E11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" t="s">
-        <v>97</v>
-      </c>
-      <c r="B12" s="6">
-        <v>1</v>
-      </c>
-      <c r="C12" s="6">
-        <v>1</v>
-      </c>
-      <c r="D12" s="6">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" t="s">
-        <v>99</v>
-      </c>
-      <c r="B13" s="15">
-        <f>B10*B11*B12</f>
-        <v>1.37934139816</v>
-      </c>
-      <c r="C13" s="15">
-        <f>C10*C11*C12</f>
-        <v>17.165820072622225</v>
-      </c>
-      <c r="D13" s="15">
-        <f>D10*D11*D12</f>
-        <v>106.91175848173336</v>
-      </c>
-      <c r="E13" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" t="s">
-        <v>101</v>
-      </c>
-      <c r="B14" s="15">
-        <f>B13*12</f>
-        <v>16.552096777919999</v>
-      </c>
-      <c r="C14" s="15">
-        <f>C13*12</f>
-        <v>205.9898408714667</v>
-      </c>
-      <c r="D14" s="15">
-        <f>D13*12</f>
-        <v>1282.9411017808002</v>
-      </c>
-      <c r="E14" t="s">
-        <v>102</v>
-      </c>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3623,151 +5207,151 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="36.625" customWidth="1"/>
-    <col min="2" max="2" width="14.125" customWidth="1"/>
-    <col min="3" max="3" width="11.4375" customWidth="1"/>
-    <col min="4" max="4" width="13.4375" customWidth="1"/>
-    <col min="5" max="5" width="10.75" customWidth="1"/>
-    <col min="6" max="6" width="12.8125" customWidth="1"/>
-    <col min="7" max="7" width="12" customWidth="1"/>
-    <col min="8" max="8" width="42" customWidth="1"/>
+    <col min="1" max="1" width="17.1875" customWidth="1"/>
+    <col min="2" max="2" width="19.3125" customWidth="1"/>
+    <col min="3" max="3" width="17.1875" customWidth="1"/>
+    <col min="4" max="4" width="18.25" customWidth="1"/>
+    <col min="5" max="5" width="15.125" customWidth="1"/>
+    <col min="6" max="6" width="18.25" customWidth="1"/>
+    <col min="7" max="7" width="17.1875" customWidth="1"/>
+    <col min="8" max="8" width="52.5625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.649999999999999">
-      <c r="A1" s="20" t="s">
-        <v>103</v>
-      </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="23"/>
-    </row>
-    <row r="3" spans="1:8" ht="27.75">
-      <c r="A3" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C3" s="3" t="s">
+    <row r="1" spans="1:8" ht="20" customHeight="1">
+      <c r="A1" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="52"/>
+    </row>
+    <row r="2" spans="1:8" ht="14.25">
+      <c r="A2" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="G2" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="14.25">
+      <c r="A3" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="40">
+        <f>'06_Воронка'!B5</f>
+        <v>42.667081111111109</v>
+      </c>
+      <c r="C3" s="40">
+        <f>'06_Воронка'!B7</f>
+        <v>0.85334162222222221</v>
+      </c>
+      <c r="D3" s="40">
+        <f>'06_Воронка'!B9</f>
+        <v>2.5600248666666665E-2</v>
+      </c>
+      <c r="E3" s="42">
+        <f>'06_Воронка'!B10</f>
+        <v>53.88</v>
+      </c>
+      <c r="F3" s="42">
+        <f>'06_Воронка'!B12</f>
+        <v>1.37934139816</v>
+      </c>
+      <c r="G3" s="42">
+        <f>'06_Воронка'!B13</f>
+        <v>16.552096777919999</v>
+      </c>
+      <c r="H3" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="G3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:8" ht="14.25">
+      <c r="A4" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="40">
+        <f>'06_Воронка'!C5</f>
+        <v>85.334162222222218</v>
+      </c>
+      <c r="C4" s="40">
+        <f>'06_Воронка'!C7</f>
+        <v>3.4133664888888888</v>
+      </c>
+      <c r="D4" s="40">
+        <f>'06_Воронка'!C9</f>
+        <v>0.17066832444444446</v>
+      </c>
+      <c r="E4" s="42">
+        <f>'06_Воронка'!C10</f>
+        <v>100.58</v>
+      </c>
+      <c r="F4" s="42">
+        <f>'06_Воронка'!C12</f>
+        <v>17.165820072622225</v>
+      </c>
+      <c r="G4" s="42">
+        <f>'06_Воронка'!C13</f>
+        <v>205.9898408714667</v>
+      </c>
+      <c r="H4" s="21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="14.25">
+      <c r="A5" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="41">
+        <f>'06_Воронка'!D5</f>
+        <v>128.00124333333332</v>
+      </c>
+      <c r="C5" s="41">
+        <f>'06_Воронка'!D7</f>
+        <v>8.960087033333334</v>
+      </c>
+      <c r="D5" s="41">
+        <f>'06_Воронка'!D9</f>
+        <v>0.71680696266666677</v>
+      </c>
+      <c r="E5" s="43">
+        <f>'06_Воронка'!D10</f>
+        <v>149.15</v>
+      </c>
+      <c r="F5" s="43">
+        <f>'06_Воронка'!D12</f>
+        <v>106.91175848173336</v>
+      </c>
+      <c r="G5" s="43">
+        <f>'06_Воронка'!D13</f>
+        <v>1282.9411017808002</v>
+      </c>
+      <c r="H5" s="14" t="s">
         <v>101</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" t="s">
-        <v>82</v>
-      </c>
-      <c r="B4" s="12">
-        <f>'06_Воронка'!B6</f>
-        <v>42.667081111111109</v>
-      </c>
-      <c r="C4" s="12">
-        <f>'06_Воронка'!B8</f>
-        <v>0.85334162222222221</v>
-      </c>
-      <c r="D4" s="12">
-        <f>'06_Воронка'!B10</f>
-        <v>2.5600248666666665E-2</v>
-      </c>
-      <c r="E4" s="7">
-        <f>'06_Воронка'!B11</f>
-        <v>53.88</v>
-      </c>
-      <c r="F4" s="7">
-        <f>'06_Воронка'!B13</f>
-        <v>1.37934139816</v>
-      </c>
-      <c r="G4" s="7">
-        <f>'06_Воронка'!B14</f>
-        <v>16.552096777919999</v>
-      </c>
-      <c r="H4" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="12">
-        <f>'06_Воронка'!C6</f>
-        <v>85.334162222222218</v>
-      </c>
-      <c r="C5" s="12">
-        <f>'06_Воронка'!C8</f>
-        <v>3.4133664888888888</v>
-      </c>
-      <c r="D5" s="12">
-        <f>'06_Воронка'!C10</f>
-        <v>0.17066832444444446</v>
-      </c>
-      <c r="E5" s="7">
-        <f>'06_Воронка'!C11</f>
-        <v>100.58</v>
-      </c>
-      <c r="F5" s="7">
-        <f>'06_Воронка'!C13</f>
-        <v>17.165820072622225</v>
-      </c>
-      <c r="G5" s="7">
-        <f>'06_Воронка'!C14</f>
-        <v>205.9898408714667</v>
-      </c>
-      <c r="H5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>84</v>
-      </c>
-      <c r="B6" s="12">
-        <f>'06_Воронка'!D6</f>
-        <v>128.00124333333332</v>
-      </c>
-      <c r="C6" s="12">
-        <f>'06_Воронка'!D8</f>
-        <v>8.960087033333334</v>
-      </c>
-      <c r="D6" s="12">
-        <f>'06_Воронка'!D10</f>
-        <v>0.71680696266666677</v>
-      </c>
-      <c r="E6" s="7">
-        <f>'06_Воронка'!D11</f>
-        <v>149.15</v>
-      </c>
-      <c r="F6" s="7">
-        <f>'06_Воронка'!D13</f>
-        <v>106.91175848173336</v>
-      </c>
-      <c r="G6" s="7">
-        <f>'06_Воронка'!D14</f>
-        <v>1282.9411017808002</v>
-      </c>
-      <c r="H6" t="s">
-        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -3783,120 +5367,161 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="13.4375" customWidth="1"/>
-    <col min="3" max="3" width="48" customWidth="1"/>
+    <col min="1" max="1" width="39.25" customWidth="1"/>
+    <col min="2" max="2" width="14.0625" customWidth="1"/>
+    <col min="3" max="3" width="52.5625" customWidth="1"/>
+    <col min="4" max="8" width="10.5625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="17.649999999999999">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:8" ht="20" customHeight="1">
+      <c r="A1" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
+      <c r="D1" s="50"/>
+      <c r="E1" s="50"/>
+      <c r="F1" s="50"/>
+      <c r="G1" s="50"/>
+      <c r="H1" s="50"/>
+    </row>
+    <row r="2" spans="1:8" ht="14.25">
+      <c r="A2" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="1:8" ht="14.25">
+      <c r="A3" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B3" s="34">
+        <f>AVERAGE('05_Нормализация'!F3:F14)</f>
+        <v>62.160887270528953</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+    </row>
+    <row r="4" spans="1:8" ht="14.25">
+      <c r="A4" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B4" s="34">
+        <f>MAX('05_Нормализация'!F3:F14)</f>
+        <v>85.849666164118034</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" ht="14.25">
+      <c r="A5" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B5" s="36">
+        <f>AVERAGE('04_Wordstat'!H3:H14)</f>
+        <v>1066.6770277777778</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+    </row>
+    <row r="6" spans="1:8" ht="14.25">
+      <c r="A6" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B6" s="36">
+        <f>'06_Воронка'!C12</f>
+        <v>17.165820072622225</v>
+      </c>
+      <c r="C6" s="44" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-    </row>
-    <row r="3" spans="1:8" ht="13.9">
-      <c r="A3" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="2" t="s">
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+    </row>
+    <row r="7" spans="1:8" ht="14.25">
+      <c r="A7" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B4" s="16">
-        <f>AVERAGE('05_Нормализация'!F4:F15)</f>
-        <v>62.160887270528953</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="B7" s="36">
+        <f>'06_Воронка'!C13</f>
+        <v>205.9898408714667</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:8" ht="14.25">
+      <c r="A8" s="3" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="27">
-      <c r="A5" s="2" t="s">
+      <c r="B8" s="45" t="str">
+        <f>TEXT('06_Воронка'!B13,"# ##0")&amp;" — "&amp;TEXT('06_Воронка'!D13,"# ##0")</f>
+        <v>17 — 1 283</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:8" ht="14.25">
+      <c r="A9" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B5" s="16">
-        <f>MAX('05_Нормализация'!F4:F15)</f>
-        <v>85.849666164118034</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="B9" s="46" t="str">
+        <f>IF(B3&gt;=75,"высокий",IF(B3&gt;=45,"средний","низкий"))</f>
+        <v>средний</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="B6" s="17">
-        <f>AVERAGE('04_Wordstat'!H4:H15)</f>
-        <v>1066.6770277777778</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="B7" s="17">
-        <f>'06_Воронка'!C13</f>
-        <v>17.165820072622225</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B8" s="17">
-        <f>'06_Воронка'!C14</f>
-        <v>205.9898408714667</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="27">
-      <c r="A9" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B9" s="18" t="str">
-        <f>TEXT('06_Воронка'!B14,"# ##0")&amp;" — "&amp;TEXT('06_Воронка'!D14,"# ##0")</f>
-        <v>17 — 1 283</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B10" s="18" t="str">
-        <f>IF(B4&gt;=75,"высокий",IF(B4&gt;=45,"средний","низкий"))</f>
-        <v>средний</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>123</v>
-      </c>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
